--- a/Wage-Type-Mapping.xlsx
+++ b/Wage-Type-Mapping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANANTH\OneDrive - FUTURE MILEZ DMCC\FM\1. Automations\SF upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://futuremilz-my.sharepoint.com/personal/ananth_futuremilez_com/Documents/FM/1. Automations/SF upload/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0A1FD0-FF80-47A3-B1A1-17B33A8CAAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{FF0A1FD0-FF80-47A3-B1A1-17B33A8CAAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2423ABA5-3F7F-4C74-A5AC-A4D23D7744F5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D4DF029B-0D1F-460A-96F5-A2E6067D38C1}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$185</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2291,7 +2291,7 @@
         <v>180</v>
       </c>
       <c r="B151" s="2">
-        <v>2012</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
